--- a/исправления внести/общий.xlsx
+++ b/исправления внести/общий.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA961E4-0F6B-4C7D-89D3-CE83EA10AED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CD38DC-124A-4A00-BDEB-94FA2B82493A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>бенефисный </t>
   </si>
@@ -91,6 +88,9 @@
   </si>
   <si>
     <t>безальтернативным</t>
+  </si>
+  <si>
+    <t xml:space="preserve">реагирует </t>
   </si>
 </sst>
 </file>
@@ -424,48 +424,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -473,7 +473,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -489,7 +489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -497,7 +497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -505,7 +505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -513,7 +513,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -521,14 +521,19 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/общий.xlsx
+++ b/исправления внести/общий.xlsx
@@ -1,31 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CD38DC-124A-4A00-BDEB-94FA2B82493A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCA2ABA-D9F1-4DFD-8400-B50C63A2CB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="91">
   <si>
     <t>бенефисный </t>
   </si>
@@ -91,6 +95,213 @@
   </si>
   <si>
     <t xml:space="preserve">реагирует </t>
+  </si>
+  <si>
+    <t>мемуары</t>
+  </si>
+  <si>
+    <t>сенсационных</t>
+  </si>
+  <si>
+    <t>айсберга</t>
+  </si>
+  <si>
+    <t>Жанр</t>
+  </si>
+  <si>
+    <t>памфлет.</t>
+  </si>
+  <si>
+    <t>поинтересовался</t>
+  </si>
+  <si>
+    <t>памфлетом</t>
+  </si>
+  <si>
+    <t>полемической</t>
+  </si>
+  <si>
+    <t>общественно-политическим</t>
+  </si>
+  <si>
+    <t>хроники</t>
+  </si>
+  <si>
+    <t>«адресатов»</t>
+  </si>
+  <si>
+    <t>дореволюционной</t>
+  </si>
+  <si>
+    <t>параллелей,</t>
+  </si>
+  <si>
+    <t>классик</t>
+  </si>
+  <si>
+    <t>цари ненастоящие</t>
+  </si>
+  <si>
+    <t>политик</t>
+  </si>
+  <si>
+    <t>дипломат</t>
+  </si>
+  <si>
+    <t>плутократиям</t>
+  </si>
+  <si>
+    <t>влиятельного класса</t>
+  </si>
+  <si>
+    <t>инкубаторе</t>
+  </si>
+  <si>
+    <t>штампуют:</t>
+  </si>
+  <si>
+    <t>кулисами</t>
+  </si>
+  <si>
+    <t>манера</t>
+  </si>
+  <si>
+    <t>привилегией.</t>
+  </si>
+  <si>
+    <t>штрихи</t>
+  </si>
+  <si>
+    <t>патриотами</t>
+  </si>
+  <si>
+    <t>демократов</t>
+  </si>
+  <si>
+    <t>сиюминутной</t>
+  </si>
+  <si>
+    <t>ветераны</t>
+  </si>
+  <si>
+    <t>демократического</t>
+  </si>
+  <si>
+    <t>дискредитации</t>
+  </si>
+  <si>
+    <t>процентов.</t>
+  </si>
+  <si>
+    <t>непрофессиональное</t>
+  </si>
+  <si>
+    <t>гигант</t>
+  </si>
+  <si>
+    <t>системообразующая</t>
+  </si>
+  <si>
+    <t>жанровое</t>
+  </si>
+  <si>
+    <t>библейский</t>
+  </si>
+  <si>
+    <t>актуален:</t>
+  </si>
+  <si>
+    <t>проинвестировать</t>
+  </si>
+  <si>
+    <t>сырьевая распределение</t>
+  </si>
+  <si>
+    <t>инструмента,</t>
+  </si>
+  <si>
+    <t>сверхконцентрации</t>
+  </si>
+  <si>
+    <t>офшоризации</t>
+  </si>
+  <si>
+    <t>«реформировал»</t>
+  </si>
+  <si>
+    <t>командует</t>
+  </si>
+  <si>
+    <t>бюджетом</t>
+  </si>
+  <si>
+    <t>банкротом</t>
+  </si>
+  <si>
+    <t>госфинансирование.</t>
+  </si>
+  <si>
+    <t>оригинала.</t>
+  </si>
+  <si>
+    <t>психику</t>
+  </si>
+  <si>
+    <t>бюджетников,</t>
+  </si>
+  <si>
+    <t>политических</t>
+  </si>
+  <si>
+    <t>неадекватов</t>
+  </si>
+  <si>
+    <t>дрессированным</t>
+  </si>
+  <si>
+    <t>отрепетированными</t>
+  </si>
+  <si>
+    <t>президентский</t>
+  </si>
+  <si>
+    <t>бутафория.</t>
+  </si>
+  <si>
+    <t>телерепортаже</t>
+  </si>
+  <si>
+    <t>одногруппников,</t>
+  </si>
+  <si>
+    <t>одноклубников</t>
+  </si>
+  <si>
+    <t>депутатом</t>
+  </si>
+  <si>
+    <t>шунтирования</t>
+  </si>
+  <si>
+    <t>«театрализованный»</t>
+  </si>
+  <si>
+    <t>астрономические</t>
+  </si>
+  <si>
+    <t>декларируют</t>
+  </si>
+  <si>
+    <t>социалку</t>
+  </si>
+  <si>
+    <t>чертежа распила</t>
+  </si>
+  <si>
+    <t>Холуизм</t>
+  </si>
+  <si>
+    <t>персонаж</t>
   </si>
 </sst>
 </file>
@@ -424,48 +635,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D83"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.90625" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -473,7 +684,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
@@ -481,7 +692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -489,7 +700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -497,7 +708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -505,7 +716,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>16</v>
       </c>
@@ -513,7 +724,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -521,19 +732,378 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EDE5B9-17C8-4B16-B1F4-4DEF72388571}">
+  <dimension ref="A2:E3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
